--- a/docs/DTT-Assessment-Hour-Log.xlsx
+++ b/docs/DTT-Assessment-Hour-Log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46862959-F641-4A37-AC0A-C58657176045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBD5380-57A9-4E28-ACFB-4725F5BFD2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2620,7 +2620,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="11">
-        <f ca="1">SUMIF(E4:E47,"&lt;&gt;x",B4:B42)</f>
+        <f>SUMIF(E4:E47,"&lt;&gt;x",B4:B47)</f>
         <v>31</v>
       </c>
       <c r="C49" s="3"/>

--- a/docs/DTT-Assessment-Hour-Log.xlsx
+++ b/docs/DTT-Assessment-Hour-Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBD5380-57A9-4E28-ACFB-4725F5BFD2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABBC776-4DA7-47C4-B4FC-02DF17013589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
   <si>
     <t>Subject</t>
   </si>
@@ -329,6 +329,12 @@
   </si>
   <si>
     <t>Fixed updateHouse to also fetch selectedHouse after update so detail page shows latest data</t>
+  </si>
+  <si>
+    <t>Mobile responsiveness</t>
+  </si>
+  <si>
+    <t>Made all pages and components mobile responsive using media queries.</t>
   </si>
 </sst>
 </file>
@@ -2575,10 +2581,18 @@
       <c r="E42" s="16"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="5"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="12"/>
+      <c r="A43" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="18">
+        <v>3</v>
+      </c>
+      <c r="C43" s="14">
+        <v>46059</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>93</v>
+      </c>
       <c r="E43" s="16"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
@@ -2621,7 +2635,7 @@
       </c>
       <c r="B49" s="11">
         <f>SUMIF(E4:E47,"&lt;&gt;x",B4:B47)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>

--- a/docs/DTT-Assessment-Hour-Log.xlsx
+++ b/docs/DTT-Assessment-Hour-Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABBC776-4DA7-47C4-B4FC-02DF17013589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA022150-F075-4D8D-916D-39AC1704BF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
   <si>
     <t>Subject</t>
   </si>
@@ -335,6 +335,27 @@
   </si>
   <si>
     <t>Made all pages and components mobile responsive using media queries.</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Empty state</t>
+  </si>
+  <si>
+    <t>Added empty state image from DTT assets when search returns no results</t>
+  </si>
+  <si>
+    <t>Final code cleanup</t>
+  </si>
+  <si>
+    <t>checked for unused CSS classes and imports, verified all hardcoded values replaced with CSS variables</t>
+  </si>
+  <si>
+    <t>README</t>
+  </si>
+  <si>
+    <t>Added README with project description, tech stack, features, installation instructions and environment variables setup</t>
   </si>
 </sst>
 </file>
@@ -450,7 +471,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -591,6 +612,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
@@ -609,7 +641,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -660,6 +692,9 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2202,7 +2237,9 @@
       <c r="D18" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
@@ -2266,7 +2303,9 @@
       <c r="D22" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
@@ -2330,7 +2369,9 @@
       <c r="D26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="16"/>
+      <c r="E26" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
@@ -2443,7 +2484,7 @@
         <v>72</v>
       </c>
       <c r="E33" s="16"/>
-      <c r="F33" s="6"/>
+      <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="5" t="s">
@@ -2459,6 +2500,7 @@
         <v>74</v>
       </c>
       <c r="E34" s="16"/>
+      <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="5" t="s">
@@ -2474,6 +2516,7 @@
         <v>76</v>
       </c>
       <c r="E35" s="16"/>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="5" t="s">
@@ -2489,6 +2532,7 @@
         <v>79</v>
       </c>
       <c r="E36" s="16"/>
+      <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="5" t="s">
@@ -2504,6 +2548,7 @@
         <v>81</v>
       </c>
       <c r="E37" s="16"/>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="5" t="s">
@@ -2519,6 +2564,7 @@
         <v>83</v>
       </c>
       <c r="E38" s="16"/>
+      <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="5" t="s">
@@ -2534,6 +2580,7 @@
         <v>85</v>
       </c>
       <c r="E39" s="16"/>
+      <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A40" s="5" t="s">
@@ -2549,6 +2596,7 @@
         <v>87</v>
       </c>
       <c r="E40" s="16"/>
+      <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="5" t="s">
@@ -2564,6 +2612,7 @@
         <v>89</v>
       </c>
       <c r="E41" s="16"/>
+      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="5" t="s">
@@ -2579,42 +2628,73 @@
         <v>91</v>
       </c>
       <c r="E42" s="16"/>
+      <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A43" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A44" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B44" s="18">
         <v>3</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C44" s="14">
         <v>46059</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D44" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="5"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="16"/>
+      <c r="E44" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A45" s="5"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="12"/>
+      <c r="A45" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="18">
+        <v>1</v>
+      </c>
+      <c r="C45" s="14">
+        <v>46059</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="E45" s="16"/>
+      <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="5"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="12"/>
+      <c r="A46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="14">
+        <v>46059</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="E46" s="16"/>
+      <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="5"/>
@@ -2622,6 +2702,7 @@
       <c r="C47" s="14"/>
       <c r="D47" s="12"/>
       <c r="E47" s="16"/>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="8"/>
@@ -2635,7 +2716,7 @@
       </c>
       <c r="B49" s="11">
         <f>SUMIF(E4:E47,"&lt;&gt;x",B4:B47)</f>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
